--- a/docs/assets_output/03_DV_construction.xlsx
+++ b/docs/assets_output/03_DV_construction.xlsx
@@ -1,38 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -40,18 +45,94 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -339,10 +420,233 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Table 3.1: Route outcomes after 3.08 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Route outcome</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Insecure outcome</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1278</v>
+      </c>
+      <c r="C3" t="n">
+        <v>38.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Returned to homelessness</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1012</v>
+      </c>
+      <c r="C4" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Independent accommodation</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>963</v>
+      </c>
+      <c r="C5" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Died</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>80</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Table 3.2: People with multiple returns during 7.5 yrs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Multiple returns</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3460</v>
+      </c>
+      <c r="C10" t="n">
+        <v>92.09999999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B11" t="n">
+        <v>295</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Table 3.3: People with a route in top 10% of route durations</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Had a longer-term route</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3250</v>
+      </c>
+      <c r="C15" t="n">
+        <v>86.59999999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B16" t="n">
+        <v>505</v>
+      </c>
+      <c r="C16" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Table 3.4: Returns within 2 years after moving to independent accommodation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Returned within 2y</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1022</v>
+      </c>
+      <c r="C20" t="n">
+        <v>97.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>24</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/assets_output/03_DV_construction.xlsx
+++ b/docs/assets_output/03_DV_construction.xlsx
@@ -1,37 +1,93 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+  <si>
+    <t>Table 3.1: Route outcomes after 3.08 years</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>pct</t>
+  </si>
+  <si>
+    <t>Route outcome</t>
+  </si>
+  <si>
+    <t>Independent accommodation</t>
+  </si>
+  <si>
+    <t>Insecure outcome</t>
+  </si>
+  <si>
+    <t>Returned to homelessness</t>
+  </si>
+  <si>
+    <t>Died</t>
+  </si>
+  <si>
+    <t>Table 3.2: People with multiple returns during 7.5 yrs</t>
+  </si>
+  <si>
+    <t>Multiple returns</t>
+  </si>
+  <si>
+    <t>Table 3.3: People with a route in top 10% of route durations</t>
+  </si>
+  <si>
+    <t>Had a longer-term route</t>
+  </si>
+  <si>
+    <t>Table 3.4: Returns within 2 years after moving to independent accommodation</t>
+  </si>
+  <si>
+    <t>Returned within 2y</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +102,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,233 +418,185 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Table 3.1: Route outcomes after 3.08 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Route outcome</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Insecure outcome</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1278</v>
-      </c>
-      <c r="C3" t="n">
-        <v>38.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Returned to homelessness</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1012</v>
-      </c>
-      <c r="C4" t="n">
-        <v>30.4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Independent accommodation</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>963</v>
-      </c>
-      <c r="C5" t="n">
-        <v>28.9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Died</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>80</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Table 3.2: People with multiple returns during 7.5 yrs</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Multiple returns</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>1217</v>
+      </c>
+      <c r="C3">
+        <v>46.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>832</v>
+      </c>
+      <c r="C4">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>517</v>
+      </c>
+      <c r="C5">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>66</v>
+      </c>
+      <c r="C6">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>3460</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>92.09999999999999</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3">
       <c r="A11" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>295</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>7.9</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Table 3.3: People with a route in top 10% of route durations</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Had a longer-term route</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>3250</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>86.59999999999999</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3">
       <c r="A16" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>505</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>13.4</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Table 3.4: Returns within 2 years after moving to independent accommodation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Returned within 2y</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20">
         <v>1022</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>97.7</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
+    <row r="21" spans="1:3">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21">
         <v>24</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>2.3</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/assets_output/03_DV_construction.xlsx
+++ b/docs/assets_output/03_DV_construction.xlsx
@@ -1,93 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
-  <si>
-    <t>Table 3.1: Route outcomes after 3.08 years</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>pct</t>
-  </si>
-  <si>
-    <t>Route outcome</t>
-  </si>
-  <si>
-    <t>Independent accommodation</t>
-  </si>
-  <si>
-    <t>Insecure outcome</t>
-  </si>
-  <si>
-    <t>Returned to homelessness</t>
-  </si>
-  <si>
-    <t>Died</t>
-  </si>
-  <si>
-    <t>Table 3.2: People with multiple returns during 7.5 yrs</t>
-  </si>
-  <si>
-    <t>Multiple returns</t>
-  </si>
-  <si>
-    <t>Table 3.3: People with a route in top 10% of route durations</t>
-  </si>
-  <si>
-    <t>Had a longer-term route</t>
-  </si>
-  <si>
-    <t>Table 3.4: Returns within 2 years after moving to independent accommodation</t>
-  </si>
-  <si>
-    <t>Returned within 2y</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -102,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -418,185 +420,233 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Table 3.1: Route outcomes after 3.08 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Route outcome</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Independent accommodation</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>1217</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>46.2</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Insecure outcome</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>832</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>31.6</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Returned to homelessness</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>517</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>19.6</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6">
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Died</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>66</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Table 3.2: People with multiple returns during 7.5 yrs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Multiple returns</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>3460</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>92.09999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11">
       <c r="A11" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>295</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>7.9</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Table 3.3: People with a route in top 10% of route durations</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Had a longer-term route</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>3250</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>86.59999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16">
       <c r="A16" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>505</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>13.4</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Table 3.4: Returns within 2 years after moving to independent accommodation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Returned within 2y</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>1022</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>97.7</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>24</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>2.3</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/assets_output/03_DV_construction.xlsx
+++ b/docs/assets_output/03_DV_construction.xlsx
@@ -1,37 +1,153 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="36">
+  <si>
+    <t>Table 3.1: Entry point into BAHSA services</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>pct</t>
+  </si>
+  <si>
+    <t>pathway_type</t>
+  </si>
+  <si>
+    <t>pathway_level</t>
+  </si>
+  <si>
+    <t>Homelessness</t>
+  </si>
+  <si>
+    <t>Substance Misuse</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Table 3.2: Route outcomes after 3.08 years</t>
+  </si>
+  <si>
+    <t>Route outcome</t>
+  </si>
+  <si>
+    <t>Independent accommodation</t>
+  </si>
+  <si>
+    <t>Insecure outcome</t>
+  </si>
+  <si>
+    <t>Returned to homelessness</t>
+  </si>
+  <si>
+    <t>Died</t>
+  </si>
+  <si>
+    <t>Table 3.3: Route outcomes after 3.08 years</t>
+  </si>
+  <si>
+    <t>Table 3.4: People with multiple returns during 7.5 yrs</t>
+  </si>
+  <si>
+    <t>Multiple returns</t>
+  </si>
+  <si>
+    <t>Table 3.5: People with a route in top 10% of route durations</t>
+  </si>
+  <si>
+    <t>Had a longer-term route</t>
+  </si>
+  <si>
+    <t>Table 3.6: Returns within 2 years after moving to independent accommodation</t>
+  </si>
+  <si>
+    <t>Returned within 2y</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Table 3.7.1: All placements</t>
+  </si>
+  <si>
+    <t>ended</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Ended</t>
+  </si>
+  <si>
+    <t>Table 3.7.3: Placement outcomes</t>
+  </si>
+  <si>
+    <t>pl_outcome</t>
+  </si>
+  <si>
+    <t>Internal move: forwards</t>
+  </si>
+  <si>
+    <t>Internal move: sideways</t>
+  </si>
+  <si>
+    <t>Internal move: backwards</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +162,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,233 +478,555 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D59"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Table 3.1: Route outcomes after 3.08 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Route outcome</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Independent accommodation</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>2481</v>
+      </c>
+      <c r="D3">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>389</v>
+      </c>
+      <c r="D4">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>206</v>
+      </c>
+      <c r="D5">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>917</v>
+      </c>
+      <c r="D6">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>844</v>
+      </c>
+      <c r="D7">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8">
+        <v>235</v>
+      </c>
+      <c r="D8">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>5072</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <v>1148</v>
+      </c>
+      <c r="C13">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>1093</v>
+      </c>
+      <c r="C14">
+        <v>32.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <v>1012</v>
+      </c>
+      <c r="C15">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <v>80</v>
+      </c>
+      <c r="C16">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17">
+        <v>3333</v>
+      </c>
+      <c r="C17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21">
         <v>1217</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C21">
         <v>46.2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Insecure outcome</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="22" spans="1:3">
+      <c r="A22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22">
         <v>832</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C22">
         <v>31.6</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Returned to homelessness</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="23" spans="1:3">
+      <c r="A23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23">
         <v>517</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C23">
         <v>19.6</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Died</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="24" spans="1:3">
+      <c r="A24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24">
         <v>66</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C24">
         <v>2.5</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Table 3.2: People with multiple returns during 7.5 yrs</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Multiple returns</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="b">
+    <row r="25" spans="1:3">
+      <c r="A25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25">
+        <v>2632</v>
+      </c>
+      <c r="C25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B29">
         <v>3460</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C29">
         <v>92.09999999999999</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="b">
+    <row r="30" spans="1:3">
+      <c r="A30" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B30">
         <v>295</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C30">
         <v>7.9</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Table 3.3: People with a route in top 10% of route durations</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Had a longer-term route</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="b">
+    <row r="31" spans="1:3">
+      <c r="A31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31">
+        <v>3755</v>
+      </c>
+      <c r="C31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B35">
         <v>3250</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C35">
         <v>86.59999999999999</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="b">
+    <row r="36" spans="1:3">
+      <c r="A36" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B36">
         <v>505</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C36">
         <v>13.4</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Table 3.4: Returns within 2 years after moving to independent accommodation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Returned within 2y</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
+    <row r="37" spans="1:3">
+      <c r="A37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37">
+        <v>3755</v>
+      </c>
+      <c r="C37">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41">
         <v>1022</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C41">
         <v>97.7</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
+    <row r="42" spans="1:3">
+      <c r="A42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B42">
         <v>24</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C42">
         <v>2.3</v>
       </c>
     </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B46">
+        <v>762</v>
+      </c>
+      <c r="C46">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47">
+        <v>7708</v>
+      </c>
+      <c r="C47">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48">
+        <v>8470</v>
+      </c>
+      <c r="C48">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B52">
+        <v>1562</v>
+      </c>
+      <c r="C52">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B53">
+        <v>1225</v>
+      </c>
+      <c r="C53">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B54">
+        <v>1164</v>
+      </c>
+      <c r="C54">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B55">
+        <v>744</v>
+      </c>
+      <c r="C55">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B56">
+        <v>653</v>
+      </c>
+      <c r="C56">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57">
+        <v>638</v>
+      </c>
+      <c r="C57">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B58">
+        <v>117</v>
+      </c>
+      <c r="C58">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59">
+        <v>6103</v>
+      </c>
+      <c r="C59">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A7:A8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/assets_output/03_DV_construction.xlsx
+++ b/docs/assets_output/03_DV_construction.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="37">
   <si>
     <t>Table 3.1: Entry point into BAHSA services</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>Internal move: backwards</t>
+  </si>
+  <si>
+    <t>Insecure outcome (external)</t>
   </si>
 </sst>
 </file>
@@ -991,7 +994,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="1" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B57">
         <v>638</v>
